--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.87147277415647</v>
+        <v>5.829114325800426</v>
       </c>
       <c r="D2" t="n">
-        <v>34.98359682054348</v>
+        <v>5.684834483338316</v>
       </c>
       <c r="E2" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F2" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.05307045418745</v>
+        <v>7.64612394880546</v>
       </c>
       <c r="D3" t="n">
-        <v>46.94691495582605</v>
+        <v>7.628873680321734</v>
       </c>
       <c r="E3" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F3" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.07662012510381</v>
+        <v>6.187450770329369</v>
       </c>
       <c r="D4" t="n">
-        <v>32.86715685908959</v>
+        <v>5.340912989602058</v>
       </c>
       <c r="E4" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F4" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.44417781918692</v>
+        <v>5.109678895617874</v>
       </c>
       <c r="D5" t="n">
-        <v>21.21320343559643</v>
+        <v>3.447145558284419</v>
       </c>
       <c r="E5" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F5" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.87864880831618</v>
+        <v>5.180280431351379</v>
       </c>
       <c r="D6" t="n">
-        <v>32.86050306649206</v>
+        <v>5.33983174830496</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F6" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.72124199624061</v>
+        <v>6.4547018243891</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20460216510445</v>
+        <v>6.208247851829473</v>
       </c>
       <c r="E7" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F7" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.41993683084661</v>
+        <v>5.430739735012574</v>
       </c>
       <c r="D8" t="n">
-        <v>12.09338662244782</v>
+        <v>1.965175326147771</v>
       </c>
       <c r="E8" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F8" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.36070533453879</v>
+        <v>7.208614616862554</v>
       </c>
       <c r="D9" t="n">
-        <v>42.66438795998368</v>
+        <v>6.932963043497348</v>
       </c>
       <c r="E9" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F9" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.52425970340158</v>
+        <v>6.910192201802757</v>
       </c>
       <c r="D10" t="n">
-        <v>39.54431290134247</v>
+        <v>6.425950846468151</v>
       </c>
       <c r="E10" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F10" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.091738094412991</v>
+        <v>0.502407440342111</v>
       </c>
       <c r="D11" t="n">
-        <v>23.13547060251855</v>
+        <v>3.759513972909264</v>
       </c>
       <c r="E11" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F11" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.65635706695465</v>
+        <v>9.694158023380131</v>
       </c>
       <c r="D12" t="n">
-        <v>56.59849132611615</v>
+        <v>9.197254840493875</v>
       </c>
       <c r="E12" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F12" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>58.00486649942255</v>
+        <v>9.425790806156165</v>
       </c>
       <c r="D13" t="n">
-        <v>55.06320535653251</v>
+        <v>8.947770870436534</v>
       </c>
       <c r="E13" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F13" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>71.20845760268827</v>
+        <v>11.57137436043684</v>
       </c>
       <c r="D14" t="n">
-        <v>68.57858159615314</v>
+        <v>11.14401950937489</v>
       </c>
       <c r="E14" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F14" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.01138741371154</v>
+        <v>4.389350454728125</v>
       </c>
       <c r="D15" t="n">
-        <v>26.812013177506</v>
+        <v>4.356952141344726</v>
       </c>
       <c r="E15" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F15" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>48.3574628593428</v>
+        <v>7.858087714643204</v>
       </c>
       <c r="D16" t="n">
-        <v>48.17887014670097</v>
+        <v>7.829066398838907</v>
       </c>
       <c r="E16" t="n">
-        <v>15.39394241234012</v>
+        <v>2.50151564200527</v>
       </c>
       <c r="F16" t="n">
-        <v>14.45579353234547</v>
+        <v>2.349066449006138</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
